--- a/MR_UKBiobank/BinaryData/Logistic/MR_res.xlsx
+++ b/MR_UKBiobank/BinaryData/Logistic/MR_res.xlsx
@@ -135,28 +135,28 @@
         <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>-1.4654131298615298</v>
+        <v>-1.4154598308652713</v>
       </c>
       <c r="D2" t="n">
-        <v>-1.7682965028446587</v>
+        <v>-1.7215128161646582</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.162529756878401</v>
+        <v>-1.1094068455658843</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1545323331546576</v>
+        <v>0.1561494822956056</v>
       </c>
       <c r="G2" t="n">
-        <v>2.4733595218194662E-21</v>
+        <v>1.2486236105487267E-19</v>
       </c>
       <c r="H2" t="n">
-        <v>0.23098254597575954</v>
+        <v>0.24281393443241095</v>
       </c>
       <c r="I2" t="n">
-        <v>0.17062339787259898</v>
+        <v>0.1787954585516345</v>
       </c>
       <c r="J2" t="n">
-        <v>0.31269413931893103</v>
+        <v>0.329754498420442</v>
       </c>
     </row>
   </sheetData>
@@ -207,28 +207,28 @@
         <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5333080947801566</v>
+        <v>0.5134829041057515</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3889818668301319</v>
+        <v>0.3737921609071785</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6776343227301813</v>
+        <v>0.6531736473043245</v>
       </c>
       <c r="F2" t="n">
-        <v>0.07363583058674729</v>
+        <v>0.0712707873462107</v>
       </c>
       <c r="G2" t="n">
-        <v>4.404623307106774E-13</v>
+        <v>5.81821895093654E-13</v>
       </c>
       <c r="H2" t="n">
-        <v>1.7045618441051134</v>
+        <v>1.6711013567307984</v>
       </c>
       <c r="I2" t="n">
-        <v>1.4754777960009646</v>
+        <v>1.4532350800062308</v>
       </c>
       <c r="J2" t="n">
-        <v>1.969213693526246</v>
+        <v>1.9216297369146509</v>
       </c>
     </row>
   </sheetData>
@@ -279,28 +279,28 @@
         <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5510020199787137</v>
+        <v>0.5250739605043107</v>
       </c>
       <c r="D2" t="n">
-        <v>0.36782024770810806</v>
+        <v>0.32948249656870465</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7341837922493193</v>
+        <v>0.7206654244399167</v>
       </c>
       <c r="F2" t="n">
-        <v>0.09346008789316612</v>
+        <v>0.09979156323245204</v>
       </c>
       <c r="G2" t="n">
-        <v>3.733531630704509E-9</v>
+        <v>1.4272413169968993E-7</v>
       </c>
       <c r="H2" t="n">
-        <v>1.7349906424413457</v>
+        <v>1.6905838801916848</v>
       </c>
       <c r="I2" t="n">
-        <v>1.4445823486466167</v>
+        <v>1.3902484839098015</v>
       </c>
       <c r="J2" t="n">
-        <v>2.083780500418815</v>
+        <v>2.0558007356542483</v>
       </c>
     </row>
   </sheetData>
@@ -351,28 +351,28 @@
         <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.20689218703478277</v>
+        <v>-0.19553556701701993</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.47838758901489886</v>
+        <v>-0.458329306350825</v>
       </c>
       <c r="E2" t="n">
-        <v>0.06460321494533336</v>
+        <v>0.06725817231678513</v>
       </c>
       <c r="F2" t="n">
-        <v>0.13851806223475313</v>
+        <v>0.13407843843561484</v>
       </c>
       <c r="G2" t="n">
-        <v>0.13527716107862248</v>
+        <v>0.14473941777014127</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8131073087721079</v>
+        <v>0.8223940929393061</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6197819297549271</v>
+        <v>0.6323392086000549</v>
       </c>
       <c r="J2" t="n">
-        <v>1.0667356756271484</v>
+        <v>1.0695715763044418</v>
       </c>
     </row>
   </sheetData>
@@ -423,28 +423,28 @@
         <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.028037395135022437</v>
+        <v>-0.02257439748884069</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.11692864848303003</v>
+        <v>-0.10962617214715019</v>
       </c>
       <c r="E2" t="n">
-        <v>0.06085385821298515</v>
+        <v>0.06447737716946882</v>
       </c>
       <c r="F2" t="n">
-        <v>0.04535268027959571</v>
+        <v>0.04441417074403546</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5364381592998023</v>
+        <v>0.6112638965987098</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9723520048868597</v>
+        <v>0.9776784976624311</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8896486686809278</v>
+        <v>0.8961690856508209</v>
       </c>
       <c r="J2" t="n">
-        <v>1.0627435915902972</v>
+        <v>1.0666014484278954</v>
       </c>
     </row>
   </sheetData>
@@ -495,28 +495,28 @@
         <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5240574231601224</v>
+        <v>0.503953099076472</v>
       </c>
       <c r="D2" t="n">
-        <v>0.39243030736688816</v>
+        <v>0.3765337575968436</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6556845389533565</v>
+        <v>0.6313724405561004</v>
       </c>
       <c r="F2" t="n">
-        <v>0.06715669173124195</v>
+        <v>0.06500986810185125</v>
       </c>
       <c r="G2" t="n">
-        <v>6.0212131366391994E-15</v>
+        <v>9.049364642008986E-15</v>
       </c>
       <c r="H2" t="n">
-        <v>1.6888662117289683</v>
+        <v>1.6552517285017625</v>
       </c>
       <c r="I2" t="n">
-        <v>1.4805746765376069</v>
+        <v>1.45722473099889</v>
       </c>
       <c r="J2" t="n">
-        <v>1.9264608035779196</v>
+        <v>1.8801892573082881</v>
       </c>
     </row>
   </sheetData>
